--- a/reports/latest/reports/Excel/Execution_Summary.xlsx
+++ b/reports/latest/reports/Excel/Execution_Summary.xlsx
@@ -484,7 +484,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -492,7 +492,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="3">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
